--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -28248,6 +28248,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1213">
+      <c r="A1213" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1213" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C1213" t="n">
+        <v>1.77499997615814</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>1.67499995231628</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>1.77499997615814</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>1.74000000953674</v>
+      </c>
+      <c r="G1213" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -28271,6 +28271,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1214">
+      <c r="A1214" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1214" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C1214" t="n">
+        <v>1.74000000953674</v>
+      </c>
+      <c r="D1214" t="n">
+        <v>1.68499994277954</v>
+      </c>
+      <c r="E1214" t="n">
+        <v>1.74000000953674</v>
+      </c>
+      <c r="F1214" t="n">
+        <v>1.74000000953674</v>
+      </c>
+      <c r="G1214" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -28294,6 +28294,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1215">
+      <c r="A1215" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1215" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C1215" t="n">
+        <v>1.74000000953674</v>
+      </c>
+      <c r="D1215" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>1.70500004291534</v>
+      </c>
+      <c r="F1215" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="G1215" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -28317,6 +28317,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1216">
+      <c r="A1216" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1216" t="n">
+        <v>8500</v>
+      </c>
+      <c r="C1216" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="D1216" t="n">
+        <v>1.69000005722046</v>
+      </c>
+      <c r="E1216" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="F1216" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="G1216" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -28158,22 +28158,22 @@
     </row>
     <row r="1209">
       <c r="A1209" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1209" t="n">
-        <v>28000</v>
+        <v>23000</v>
       </c>
       <c r="C1209" t="n">
         <v>1.79999995231628</v>
       </c>
       <c r="D1209" t="n">
-        <v>1.74000000953674</v>
+        <v>1.77999997138977</v>
       </c>
       <c r="E1209" t="n">
-        <v>1.76499998569489</v>
+        <v>1.77999997138977</v>
       </c>
       <c r="F1209" t="n">
-        <v>1.79499995708466</v>
+        <v>1.79999995231628</v>
       </c>
       <c r="G1209" t="s">
         <v>7</v>
@@ -28181,22 +28181,22 @@
     </row>
     <row r="1210">
       <c r="A1210" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1210" t="n">
-        <v>10500</v>
+        <v>28000</v>
       </c>
       <c r="C1210" t="n">
-        <v>1.79499995708466</v>
+        <v>1.79999995231628</v>
       </c>
       <c r="D1210" t="n">
         <v>1.74000000953674</v>
       </c>
       <c r="E1210" t="n">
+        <v>1.76499998569489</v>
+      </c>
+      <c r="F1210" t="n">
         <v>1.79499995708466</v>
-      </c>
-      <c r="F1210" t="n">
-        <v>1.75</v>
       </c>
       <c r="G1210" t="s">
         <v>7</v>
@@ -28204,22 +28204,22 @@
     </row>
     <row r="1211">
       <c r="A1211" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1211" t="n">
-        <v>7500</v>
+        <v>10500</v>
       </c>
       <c r="C1211" t="n">
-        <v>1.77499997615814</v>
+        <v>1.79499995708466</v>
       </c>
       <c r="D1211" t="n">
-        <v>1.72000002861023</v>
+        <v>1.74000000953674</v>
       </c>
       <c r="E1211" t="n">
+        <v>1.79499995708466</v>
+      </c>
+      <c r="F1211" t="n">
         <v>1.75</v>
-      </c>
-      <c r="F1211" t="n">
-        <v>1.73000001907349</v>
       </c>
       <c r="G1211" t="s">
         <v>7</v>
@@ -28227,22 +28227,22 @@
     </row>
     <row r="1212">
       <c r="A1212" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1212" t="n">
-        <v>1500</v>
+        <v>7500</v>
       </c>
       <c r="C1212" t="n">
         <v>1.77499997615814</v>
       </c>
       <c r="D1212" t="n">
-        <v>1.74500000476837</v>
+        <v>1.72000002861023</v>
       </c>
       <c r="E1212" t="n">
-        <v>1.77499997615814</v>
+        <v>1.75</v>
       </c>
       <c r="F1212" t="n">
-        <v>1.74500000476837</v>
+        <v>1.73000001907349</v>
       </c>
       <c r="G1212" t="s">
         <v>7</v>
@@ -28250,22 +28250,22 @@
     </row>
     <row r="1213">
       <c r="A1213" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1213" t="n">
-        <v>18000</v>
+        <v>1500</v>
       </c>
       <c r="C1213" t="n">
         <v>1.77499997615814</v>
       </c>
       <c r="D1213" t="n">
-        <v>1.67499995231628</v>
+        <v>1.74500000476837</v>
       </c>
       <c r="E1213" t="n">
         <v>1.77499997615814</v>
       </c>
       <c r="F1213" t="n">
-        <v>1.74000000953674</v>
+        <v>1.74500000476837</v>
       </c>
       <c r="G1213" t="s">
         <v>7</v>
@@ -28273,19 +28273,19 @@
     </row>
     <row r="1214">
       <c r="A1214" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1214" t="n">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="C1214" t="n">
-        <v>1.74000000953674</v>
+        <v>1.77499997615814</v>
       </c>
       <c r="D1214" t="n">
-        <v>1.68499994277954</v>
+        <v>1.67499995231628</v>
       </c>
       <c r="E1214" t="n">
-        <v>1.74000000953674</v>
+        <v>1.77499997615814</v>
       </c>
       <c r="F1214" t="n">
         <v>1.74000000953674</v>
@@ -28296,22 +28296,22 @@
     </row>
     <row r="1215">
       <c r="A1215" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1215" t="n">
-        <v>6500</v>
+        <v>12000</v>
       </c>
       <c r="C1215" t="n">
         <v>1.74000000953674</v>
       </c>
       <c r="D1215" t="n">
-        <v>1.67999994754791</v>
+        <v>1.68499994277954</v>
       </c>
       <c r="E1215" t="n">
-        <v>1.70500004291534</v>
+        <v>1.74000000953674</v>
       </c>
       <c r="F1215" t="n">
-        <v>1.72000002861023</v>
+        <v>1.74000000953674</v>
       </c>
       <c r="G1215" t="s">
         <v>7</v>
@@ -28319,24 +28319,47 @@
     </row>
     <row r="1216">
       <c r="A1216" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1216" t="n">
-        <v>8500</v>
+        <v>6500</v>
       </c>
       <c r="C1216" t="n">
+        <v>1.74000000953674</v>
+      </c>
+      <c r="D1216" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="E1216" t="n">
+        <v>1.70500004291534</v>
+      </c>
+      <c r="F1216" t="n">
         <v>1.72000002861023</v>
       </c>
-      <c r="D1216" t="n">
-        <v>1.69000005722046</v>
-      </c>
-      <c r="E1216" t="n">
-        <v>1.72000002861023</v>
-      </c>
-      <c r="F1216" t="n">
-        <v>1.6599999666214</v>
-      </c>
       <c r="G1216" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1217" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C1217" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="D1217" t="n">
+        <v>1.63499999046326</v>
+      </c>
+      <c r="E1217" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="F1217" t="n">
+        <v>1.70500004291534</v>
+      </c>
+      <c r="G1217" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -32069,6 +32069,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1220">
+      <c r="A1220" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1220" t="n">
+        <v>16500</v>
+      </c>
+      <c r="C1220" t="n">
+        <v>1.72500002384186</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>1.65499997138977</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="F1220" t="n">
+        <v>1.73000001907349</v>
+      </c>
+      <c r="G1220" t="n">
+        <v>1.73000001907349</v>
+      </c>
+      <c r="H1220" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -32077,7 +32077,7 @@
         <v>16500</v>
       </c>
       <c r="C1220" t="n">
-        <v>1.72500002384186</v>
+        <v>1.73000001907349</v>
       </c>
       <c r="D1220" t="n">
         <v>1.65499997138977</v>
@@ -32092,6 +32092,32 @@
         <v>1.73000001907349</v>
       </c>
       <c r="H1220" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1221" t="n">
+        <v>25500</v>
+      </c>
+      <c r="C1221" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="F1221" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="G1221" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="H1221" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -32121,6 +32121,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1222">
+      <c r="A1222" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1222" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C1222" t="n">
+        <v>1.68499994277954</v>
+      </c>
+      <c r="D1222" t="n">
+        <v>1.62000000476837</v>
+      </c>
+      <c r="E1222" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="F1222" t="n">
+        <v>1.68499994277954</v>
+      </c>
+      <c r="G1222" t="n">
+        <v>1.68499994277954</v>
+      </c>
+      <c r="H1222" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -32147,6 +32147,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1223">
+      <c r="A1223" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1223" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C1223" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="D1223" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="E1223" t="n">
+        <v>1.64999997615814</v>
+      </c>
+      <c r="F1223" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="G1223" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="H1223" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -32225,6 +32225,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1226">
+      <c r="A1226" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1226" t="n">
+        <v>36000</v>
+      </c>
+      <c r="C1226" t="n">
+        <v>1.65499997138977</v>
+      </c>
+      <c r="D1226" t="n">
+        <v>1.59500002861023</v>
+      </c>
+      <c r="E1226" t="n">
+        <v>1.65499997138977</v>
+      </c>
+      <c r="F1226" t="n">
+        <v>1.63499999046326</v>
+      </c>
+      <c r="G1226" t="n">
+        <v>1.63499999046326</v>
+      </c>
+      <c r="H1226" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -28632,8 +28632,31 @@
       <c r="E1229" t="n">
         <v>1.53999996185303</v>
       </c>
-      <c r="F1229"/>
+      <c r="F1229" t="n">
+        <v>1.55499994754791</v>
+      </c>
       <c r="G1229" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1230" t="n">
+        <v>15500</v>
+      </c>
+      <c r="C1230" t="n">
+        <v>1.5900000333786</v>
+      </c>
+      <c r="D1230" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="E1230" t="n">
+        <v>1.55499994754791</v>
+      </c>
+      <c r="F1230"/>
+      <c r="G1230" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -28655,8 +28655,31 @@
       <c r="E1230" t="n">
         <v>1.55499994754791</v>
       </c>
-      <c r="F1230"/>
+      <c r="F1230" t="n">
+        <v>1.57000005245209</v>
+      </c>
       <c r="G1230" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1231" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C1231" t="n">
+        <v>1.56500005722046</v>
+      </c>
+      <c r="D1231" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>1.56500005722046</v>
+      </c>
+      <c r="F1231"/>
+      <c r="G1231" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -28678,8 +28678,31 @@
       <c r="E1231" t="n">
         <v>1.56500005722046</v>
       </c>
-      <c r="F1231"/>
+      <c r="F1231" t="n">
+        <v>1.55499994754791</v>
+      </c>
       <c r="G1231" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1232" t="n">
+        <v>8500</v>
+      </c>
+      <c r="C1232" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="D1232" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="E1232" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="F1232"/>
+      <c r="G1232" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -28701,8 +28701,31 @@
       <c r="E1232" t="n">
         <v>1.52999997138977</v>
       </c>
-      <c r="F1232"/>
+      <c r="F1232" t="n">
+        <v>1.5349999666214</v>
+      </c>
       <c r="G1232" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1233" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C1233" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="D1233" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="E1233" t="n">
+        <v>1.5349999666214</v>
+      </c>
+      <c r="F1233"/>
+      <c r="G1233" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -28731,6 +28731,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1234">
+      <c r="A1234" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1234" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C1234" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="D1234" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="E1234" t="n">
+        <v>1.59500002861023</v>
+      </c>
+      <c r="F1234" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="G1234" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -32511,6 +32511,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1237">
+      <c r="A1237" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1237" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C1237" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="D1237" t="n">
+        <v>1.50499999523163</v>
+      </c>
+      <c r="E1237" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="F1237" t="n">
+        <v>1.5349999666214</v>
+      </c>
+      <c r="G1237" t="n">
+        <v>1.5349999666214</v>
+      </c>
+      <c r="H1237" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -32537,6 +32537,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1238">
+      <c r="A1238" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C1238" t="n">
+        <v>1.54499995708466</v>
+      </c>
+      <c r="D1238" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="E1238" t="n">
+        <v>1.54499995708466</v>
+      </c>
+      <c r="F1238" t="n">
+        <v>1.52499997615814</v>
+      </c>
+      <c r="G1238" t="n">
+        <v>1.52499997615814</v>
+      </c>
+      <c r="H1238" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -36280,6 +36280,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1239">
+      <c r="A1239" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1239" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1239" t="n">
+        <v>1.52499997615814</v>
+      </c>
+      <c r="D1239" t="n">
+        <v>1.52499997615814</v>
+      </c>
+      <c r="E1239" t="n">
+        <v>1.52499997615814</v>
+      </c>
+      <c r="F1239" t="n">
+        <v>1.52499997615814</v>
+      </c>
+      <c r="G1239" t="n">
+        <v>1.52499997615814</v>
+      </c>
+      <c r="H1239" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1239" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1240" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1240" t="n">
+        <v>1.50499999523163</v>
+      </c>
+      <c r="D1240" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="E1240" t="n">
+        <v>1.4650000333786</v>
+      </c>
+      <c r="F1240" t="n">
+        <v>1.49500000476837</v>
+      </c>
+      <c r="G1240" t="n">
+        <v>1.49500000476837</v>
+      </c>
+      <c r="H1240" t="n">
+        <v>11500</v>
+      </c>
+      <c r="I1240" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -36338,6 +36338,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1241">
+      <c r="A1241" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1241" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1241" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="D1241" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="E1241" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="F1241" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="G1241" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="H1241" t="n">
+        <v>10500</v>
+      </c>
+      <c r="I1241" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -36367,6 +36367,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1242">
+      <c r="A1242" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1242" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1242" t="n">
+        <v>1.47500002384186</v>
+      </c>
+      <c r="D1242" t="n">
+        <v>1.47500002384186</v>
+      </c>
+      <c r="E1242" t="n">
+        <v>1.34500002861023</v>
+      </c>
+      <c r="F1242" t="n">
+        <v>1.36500000953674</v>
+      </c>
+      <c r="G1242" t="n">
+        <v>1.36500000953674</v>
+      </c>
+      <c r="H1242" t="n">
+        <v>43000</v>
+      </c>
+      <c r="I1242" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -36396,6 +36396,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1243">
+      <c r="A1243" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1243" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1243" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="D1243" t="n">
+        <v>1.35500001907349</v>
+      </c>
+      <c r="E1243" t="n">
+        <v>1.29499995708466</v>
+      </c>
+      <c r="F1243" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="G1243" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="H1243" t="n">
+        <v>23500</v>
+      </c>
+      <c r="I1243" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -36425,6 +36425,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1244">
+      <c r="A1244" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1244" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1244" t="n">
+        <v>1.29499995708466</v>
+      </c>
+      <c r="D1244" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="E1244" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="F1244" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="G1244" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="H1244" t="n">
+        <v>14500</v>
+      </c>
+      <c r="I1244" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -36454,6 +36454,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1245">
+      <c r="A1245" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1245" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1245" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="D1245" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="E1245" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="F1245" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="G1245" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="H1245" t="n">
+        <v>9500</v>
+      </c>
+      <c r="I1245" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -36483,6 +36483,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1246">
+      <c r="A1246" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1246" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1246" t="n">
+        <v>1.39499998092651</v>
+      </c>
+      <c r="D1246" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="E1246" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="F1246" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="G1246" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="H1246" t="n">
+        <v>9500</v>
+      </c>
+      <c r="I1246" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -36512,6 +36512,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1247">
+      <c r="A1247" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1247" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1247" t="n">
+        <v>1.33500003814697</v>
+      </c>
+      <c r="D1247" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="E1247" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="F1247" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="G1247" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="H1247" t="n">
+        <v>10500</v>
+      </c>
+      <c r="I1247" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DATA.MI.xlsx
+++ b/data/DATA.MI.xlsx
@@ -36541,6 +36541,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1248">
+      <c r="A1248" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1248" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1248" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="D1248" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="E1248" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="F1248" t="n">
+        <v>1.33500003814697</v>
+      </c>
+      <c r="G1248" t="n">
+        <v>1.33500003814697</v>
+      </c>
+      <c r="H1248" t="n">
+        <v>10500</v>
+      </c>
+      <c r="I1248" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
